--- a/crm/v2/lgo/integral-top200-pharmony.xlsx
+++ b/crm/v2/lgo/integral-top200-pharmony.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catalogue" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catalogue'!$A$1:$C$201</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catalogue'!$A$1:$D$201</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,12 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C201"/>
+  <dimension ref="A1:D201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="44" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -453,6 +454,11 @@
           <t>PRIX ACHAT U HT</t>
         </is>
       </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>ABANDON DE MARGE</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -468,6 +474,9 @@
       <c r="C2" s="3" t="n">
         <v>1.29</v>
       </c>
+      <c r="D2" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -483,6 +492,9 @@
       <c r="C3" s="3" t="n">
         <v>1.25</v>
       </c>
+      <c r="D3" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -498,6 +510,9 @@
       <c r="C4" s="3" t="n">
         <v>3.71</v>
       </c>
+      <c r="D4" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -513,6 +528,9 @@
       <c r="C5" s="3" t="n">
         <v>8.34</v>
       </c>
+      <c r="D5" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -528,6 +546,9 @@
       <c r="C6" s="3" t="n">
         <v>1.29</v>
       </c>
+      <c r="D6" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -543,6 +564,9 @@
       <c r="C7" s="3" t="n">
         <v>1.1</v>
       </c>
+      <c r="D7" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -558,6 +582,9 @@
       <c r="C8" s="3" t="n">
         <v>1.75</v>
       </c>
+      <c r="D8" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -571,7 +598,10 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>212.71</v>
+        <v>212.74</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -588,6 +618,9 @@
       <c r="C10" s="3" t="n">
         <v>2.34</v>
       </c>
+      <c r="D10" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -603,6 +636,9 @@
       <c r="C11" s="3" t="n">
         <v>1.61</v>
       </c>
+      <c r="D11" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -616,7 +652,10 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>157.33</v>
+        <v>157.36</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -633,6 +672,9 @@
       <c r="C13" s="3" t="n">
         <v>3.06</v>
       </c>
+      <c r="D13" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -648,6 +690,9 @@
       <c r="C14" s="3" t="n">
         <v>8.6</v>
       </c>
+      <c r="D14" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -663,6 +708,9 @@
       <c r="C15" s="3" t="n">
         <v>7.02</v>
       </c>
+      <c r="D15" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -678,6 +726,9 @@
       <c r="C16" s="3" t="n">
         <v>7.11</v>
       </c>
+      <c r="D16" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -691,7 +742,10 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>103.38</v>
+        <v>103.4</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -708,6 +762,9 @@
       <c r="C18" s="3" t="n">
         <v>1.73</v>
       </c>
+      <c r="D18" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -723,6 +780,9 @@
       <c r="C19" s="3" t="n">
         <v>1.23</v>
       </c>
+      <c r="D19" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -738,6 +798,9 @@
       <c r="C20" s="3" t="n">
         <v>1.61</v>
       </c>
+      <c r="D20" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -751,7 +814,10 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>70.48999999999999</v>
+        <v>70.51000000000001</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -768,6 +834,9 @@
       <c r="C22" s="3" t="n">
         <v>2.04</v>
       </c>
+      <c r="D22" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -783,6 +852,9 @@
       <c r="C23" s="3" t="n">
         <v>1.29</v>
       </c>
+      <c r="D23" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -798,6 +870,9 @@
       <c r="C24" s="3" t="n">
         <v>1.12</v>
       </c>
+      <c r="D24" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -813,6 +888,9 @@
       <c r="C25" s="3" t="n">
         <v>26.16</v>
       </c>
+      <c r="D25" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -828,6 +906,9 @@
       <c r="C26" s="3" t="n">
         <v>3.42</v>
       </c>
+      <c r="D26" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -843,6 +924,9 @@
       <c r="C27" s="3" t="n">
         <v>2.14</v>
       </c>
+      <c r="D27" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -858,6 +942,9 @@
       <c r="C28" s="3" t="n">
         <v>1.53</v>
       </c>
+      <c r="D28" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -873,6 +960,9 @@
       <c r="C29" s="3" t="n">
         <v>2.1</v>
       </c>
+      <c r="D29" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -888,6 +978,9 @@
       <c r="C30" s="3" t="n">
         <v>2.02</v>
       </c>
+      <c r="D30" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -901,7 +994,10 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>168.37</v>
+        <v>168.39</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -918,6 +1014,9 @@
       <c r="C32" s="3" t="n">
         <v>0.5</v>
       </c>
+      <c r="D32" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -931,7 +1030,10 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>351.98</v>
+        <v>352.02</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -948,6 +1050,9 @@
       <c r="C34" s="3" t="n">
         <v>1.23</v>
       </c>
+      <c r="D34" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -963,6 +1068,9 @@
       <c r="C35" s="3" t="n">
         <v>1.56</v>
       </c>
+      <c r="D35" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -976,7 +1084,10 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>164.42</v>
+        <v>164.44</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -993,6 +1104,9 @@
       <c r="C37" s="3" t="n">
         <v>2.24</v>
       </c>
+      <c r="D37" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -1008,6 +1122,9 @@
       <c r="C38" s="3" t="n">
         <v>5.61</v>
       </c>
+      <c r="D38" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -1021,7 +1138,10 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>7.32</v>
+        <v>7.33</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -1038,6 +1158,9 @@
       <c r="C40" s="3" t="n">
         <v>1.08</v>
       </c>
+      <c r="D40" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -1053,6 +1176,9 @@
       <c r="C41" s="3" t="n">
         <v>2.02</v>
       </c>
+      <c r="D41" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -1068,6 +1194,9 @@
       <c r="C42" s="3" t="n">
         <v>0.85</v>
       </c>
+      <c r="D42" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -1083,6 +1212,9 @@
       <c r="C43" s="3" t="n">
         <v>2.18</v>
       </c>
+      <c r="D43" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -1098,6 +1230,9 @@
       <c r="C44" s="3" t="n">
         <v>1.59</v>
       </c>
+      <c r="D44" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -1113,6 +1248,9 @@
       <c r="C45" s="3" t="n">
         <v>8.6</v>
       </c>
+      <c r="D45" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -1128,6 +1266,9 @@
       <c r="C46" s="3" t="n">
         <v>2.25</v>
       </c>
+      <c r="D46" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -1143,6 +1284,9 @@
       <c r="C47" s="3" t="n">
         <v>8.6</v>
       </c>
+      <c r="D47" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -1156,7 +1300,10 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>301.08</v>
+        <v>301.11</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -1173,6 +1320,9 @@
       <c r="C49" s="3" t="n">
         <v>1.76</v>
       </c>
+      <c r="D49" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -1186,7 +1336,10 @@
         </is>
       </c>
       <c r="C50" s="3" t="n">
-        <v>4.51</v>
+        <v>4.43</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -1201,7 +1354,10 @@
         </is>
       </c>
       <c r="C51" s="3" t="n">
-        <v>43.36</v>
+        <v>43.39</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -1218,6 +1374,9 @@
       <c r="C52" s="3" t="n">
         <v>1.15</v>
       </c>
+      <c r="D52" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -1233,6 +1392,9 @@
       <c r="C53" s="3" t="n">
         <v>2.5</v>
       </c>
+      <c r="D53" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -1248,6 +1410,9 @@
       <c r="C54" s="3" t="n">
         <v>2.72</v>
       </c>
+      <c r="D54" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -1261,7 +1426,10 @@
         </is>
       </c>
       <c r="C55" s="3" t="n">
-        <v>19.15</v>
+        <v>19.17</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -1278,6 +1446,9 @@
       <c r="C56" s="3" t="n">
         <v>4.12</v>
       </c>
+      <c r="D56" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -1293,6 +1464,9 @@
       <c r="C57" s="3" t="n">
         <v>2.27</v>
       </c>
+      <c r="D57" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -1306,7 +1480,10 @@
         </is>
       </c>
       <c r="C58" s="3" t="n">
-        <v>34.77</v>
+        <v>34.8</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -1321,7 +1498,10 @@
         </is>
       </c>
       <c r="C59" s="3" t="n">
-        <v>71.39</v>
+        <v>71.42</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -1336,7 +1516,10 @@
         </is>
       </c>
       <c r="C60" s="3" t="n">
-        <v>68.23</v>
+        <v>68.25</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -1353,6 +1536,9 @@
       <c r="C61" s="3" t="n">
         <v>3.45</v>
       </c>
+      <c r="D61" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -1368,6 +1554,9 @@
       <c r="C62" s="3" t="n">
         <v>2.17</v>
       </c>
+      <c r="D62" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -1383,6 +1572,9 @@
       <c r="C63" s="3" t="n">
         <v>0.88</v>
       </c>
+      <c r="D63" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -1398,6 +1590,9 @@
       <c r="C64" s="3" t="n">
         <v>2.14</v>
       </c>
+      <c r="D64" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -1413,6 +1608,9 @@
       <c r="C65" s="3" t="n">
         <v>1.17</v>
       </c>
+      <c r="D65" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -1426,7 +1624,10 @@
         </is>
       </c>
       <c r="C66" s="3" t="n">
-        <v>131.19</v>
+        <v>131.21</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -1443,6 +1644,9 @@
       <c r="C67" s="3" t="n">
         <v>1.42</v>
       </c>
+      <c r="D67" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -1458,6 +1662,9 @@
       <c r="C68" s="3" t="n">
         <v>2.31</v>
       </c>
+      <c r="D68" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -1473,6 +1680,9 @@
       <c r="C69" s="3" t="n">
         <v>1.5</v>
       </c>
+      <c r="D69" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -1488,6 +1698,9 @@
       <c r="C70" s="3" t="n">
         <v>0.88</v>
       </c>
+      <c r="D70" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -1503,6 +1716,9 @@
       <c r="C71" s="3" t="n">
         <v>1.35</v>
       </c>
+      <c r="D71" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -1518,6 +1734,9 @@
       <c r="C72" s="3" t="n">
         <v>6.21</v>
       </c>
+      <c r="D72" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -1533,6 +1752,9 @@
       <c r="C73" s="3" t="n">
         <v>1.95</v>
       </c>
+      <c r="D73" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -1548,6 +1770,9 @@
       <c r="C74" s="3" t="n">
         <v>4.9</v>
       </c>
+      <c r="D74" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -1563,6 +1788,9 @@
       <c r="C75" s="3" t="n">
         <v>1.51</v>
       </c>
+      <c r="D75" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -1576,7 +1804,10 @@
         </is>
       </c>
       <c r="C76" s="3" t="n">
-        <v>4.24</v>
+        <v>4.23</v>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -1593,6 +1824,9 @@
       <c r="C77" s="3" t="n">
         <v>0.88</v>
       </c>
+      <c r="D77" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -1608,6 +1842,9 @@
       <c r="C78" s="3" t="n">
         <v>0.88</v>
       </c>
+      <c r="D78" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -1623,6 +1860,9 @@
       <c r="C79" s="3" t="n">
         <v>1.23</v>
       </c>
+      <c r="D79" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -1636,7 +1876,10 @@
         </is>
       </c>
       <c r="C80" s="3" t="n">
-        <v>174.42</v>
+        <v>174.45</v>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -1653,6 +1896,9 @@
       <c r="C81" s="3" t="n">
         <v>1.12</v>
       </c>
+      <c r="D81" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -1666,7 +1912,10 @@
         </is>
       </c>
       <c r="C82" s="3" t="n">
-        <v>131.19</v>
+        <v>131.21</v>
+      </c>
+      <c r="D82" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -1681,7 +1930,10 @@
         </is>
       </c>
       <c r="C83" s="3" t="n">
-        <v>11.38</v>
+        <v>11.4</v>
+      </c>
+      <c r="D83" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -1698,6 +1950,9 @@
       <c r="C84" s="3" t="n">
         <v>4.46</v>
       </c>
+      <c r="D84" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -1713,6 +1968,9 @@
       <c r="C85" s="3" t="n">
         <v>3.69</v>
       </c>
+      <c r="D85" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -1728,6 +1986,9 @@
       <c r="C86" s="3" t="n">
         <v>1.52</v>
       </c>
+      <c r="D86" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -1741,7 +2002,10 @@
         </is>
       </c>
       <c r="C87" s="3" t="n">
-        <v>71.39</v>
+        <v>71.42</v>
+      </c>
+      <c r="D87" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -1756,7 +2020,10 @@
         </is>
       </c>
       <c r="C88" s="3" t="n">
-        <v>301.08</v>
+        <v>301.11</v>
+      </c>
+      <c r="D88" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -1773,6 +2040,9 @@
       <c r="C89" s="3" t="n">
         <v>15.92</v>
       </c>
+      <c r="D89" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -1788,6 +2058,9 @@
       <c r="C90" s="3" t="n">
         <v>2.25</v>
       </c>
+      <c r="D90" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -1803,6 +2076,9 @@
       <c r="C91" s="3" t="n">
         <v>1.78</v>
       </c>
+      <c r="D91" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -1818,6 +2094,9 @@
       <c r="C92" s="3" t="n">
         <v>1.12</v>
       </c>
+      <c r="D92" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -1833,6 +2112,9 @@
       <c r="C93" s="3" t="n">
         <v>1.49</v>
       </c>
+      <c r="D93" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -1848,6 +2130,9 @@
       <c r="C94" s="3" t="n">
         <v>1.92</v>
       </c>
+      <c r="D94" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -1863,6 +2148,9 @@
       <c r="C95" s="3" t="n">
         <v>1.26</v>
       </c>
+      <c r="D95" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -1876,7 +2164,10 @@
         </is>
       </c>
       <c r="C96" s="3" t="n">
-        <v>6.71</v>
+        <v>6.98</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -1893,6 +2184,9 @@
       <c r="C97" s="3" t="n">
         <v>7.02</v>
       </c>
+      <c r="D97" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -1908,6 +2202,9 @@
       <c r="C98" s="3" t="n">
         <v>1.13</v>
       </c>
+      <c r="D98" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -1923,6 +2220,9 @@
       <c r="C99" s="3" t="n">
         <v>3.23</v>
       </c>
+      <c r="D99" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -1938,6 +2238,9 @@
       <c r="C100" s="3" t="n">
         <v>1.38</v>
       </c>
+      <c r="D100" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -1951,7 +2254,10 @@
         </is>
       </c>
       <c r="C101" s="3" t="n">
-        <v>71.39</v>
+        <v>71.42</v>
+      </c>
+      <c r="D101" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -1968,6 +2274,9 @@
       <c r="C102" s="3" t="n">
         <v>1.42</v>
       </c>
+      <c r="D102" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -1981,7 +2290,10 @@
         </is>
       </c>
       <c r="C103" s="3" t="n">
-        <v>151.25</v>
+        <v>151.27</v>
+      </c>
+      <c r="D103" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -1998,6 +2310,9 @@
       <c r="C104" s="3" t="n">
         <v>0.88</v>
       </c>
+      <c r="D104" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -2013,6 +2328,9 @@
       <c r="C105" s="3" t="n">
         <v>2.23</v>
       </c>
+      <c r="D105" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -2028,6 +2346,9 @@
       <c r="C106" s="3" t="n">
         <v>4.92</v>
       </c>
+      <c r="D106" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -2043,6 +2364,9 @@
       <c r="C107" s="3" t="n">
         <v>1.76</v>
       </c>
+      <c r="D107" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -2058,6 +2382,9 @@
       <c r="C108" s="3" t="n">
         <v>1.25</v>
       </c>
+      <c r="D108" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -2071,7 +2398,10 @@
         </is>
       </c>
       <c r="C109" s="3" t="n">
-        <v>28.92</v>
+        <v>28.94</v>
+      </c>
+      <c r="D109" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -2088,6 +2418,9 @@
       <c r="C110" s="3" t="n">
         <v>1.03</v>
       </c>
+      <c r="D110" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -2103,6 +2436,9 @@
       <c r="C111" s="3" t="n">
         <v>2.41</v>
       </c>
+      <c r="D111" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -2118,6 +2454,9 @@
       <c r="C112" s="3" t="n">
         <v>2.02</v>
       </c>
+      <c r="D112" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -2133,6 +2472,9 @@
       <c r="C113" s="3" t="n">
         <v>2.9</v>
       </c>
+      <c r="D113" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -2148,6 +2490,9 @@
       <c r="C114" s="3" t="n">
         <v>1.48</v>
       </c>
+      <c r="D114" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -2163,6 +2508,9 @@
       <c r="C115" s="3" t="n">
         <v>3.42</v>
       </c>
+      <c r="D115" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -2178,6 +2526,9 @@
       <c r="C116" s="3" t="n">
         <v>2.7</v>
       </c>
+      <c r="D116" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -2191,7 +2542,10 @@
         </is>
       </c>
       <c r="C117" s="3" t="n">
-        <v>31.05</v>
+        <v>31.08</v>
+      </c>
+      <c r="D117" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -2208,6 +2562,9 @@
       <c r="C118" s="3" t="n">
         <v>8.52</v>
       </c>
+      <c r="D118" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -2223,6 +2580,9 @@
       <c r="C119" s="3" t="n">
         <v>1.62</v>
       </c>
+      <c r="D119" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -2238,6 +2598,9 @@
       <c r="C120" s="3" t="n">
         <v>3.52</v>
       </c>
+      <c r="D120" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -2253,6 +2616,9 @@
       <c r="C121" s="3" t="n">
         <v>32.37</v>
       </c>
+      <c r="D121" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -2268,6 +2634,9 @@
       <c r="C122" s="3" t="n">
         <v>2.59</v>
       </c>
+      <c r="D122" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -2283,6 +2652,9 @@
       <c r="C123" s="3" t="n">
         <v>52.41</v>
       </c>
+      <c r="D123" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -2298,6 +2670,9 @@
       <c r="C124" s="3" t="n">
         <v>4.81</v>
       </c>
+      <c r="D124" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -2313,6 +2688,9 @@
       <c r="C125" s="3" t="n">
         <v>52.41</v>
       </c>
+      <c r="D125" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -2328,6 +2706,9 @@
       <c r="C126" s="3" t="n">
         <v>3.44</v>
       </c>
+      <c r="D126" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -2343,6 +2724,9 @@
       <c r="C127" s="3" t="n">
         <v>3.91</v>
       </c>
+      <c r="D127" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -2358,6 +2742,9 @@
       <c r="C128" s="3" t="n">
         <v>1.63</v>
       </c>
+      <c r="D128" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -2373,6 +2760,9 @@
       <c r="C129" s="3" t="n">
         <v>2.24</v>
       </c>
+      <c r="D129" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -2386,7 +2776,10 @@
         </is>
       </c>
       <c r="C130" s="3" t="n">
-        <v>4.54</v>
+        <v>4.53</v>
+      </c>
+      <c r="D130" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="131">
@@ -2403,6 +2796,9 @@
       <c r="C131" s="3" t="n">
         <v>1.69</v>
       </c>
+      <c r="D131" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -2418,6 +2814,9 @@
       <c r="C132" s="3" t="n">
         <v>1.41</v>
       </c>
+      <c r="D132" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -2433,6 +2832,9 @@
       <c r="C133" s="3" t="n">
         <v>2.31</v>
       </c>
+      <c r="D133" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -2448,6 +2850,9 @@
       <c r="C134" s="3" t="n">
         <v>0.88</v>
       </c>
+      <c r="D134" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -2463,6 +2868,9 @@
       <c r="C135" s="3" t="n">
         <v>98.15000000000001</v>
       </c>
+      <c r="D135" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -2478,6 +2886,9 @@
       <c r="C136" s="3" t="n">
         <v>1.32</v>
       </c>
+      <c r="D136" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -2493,6 +2904,9 @@
       <c r="C137" s="3" t="n">
         <v>3.67</v>
       </c>
+      <c r="D137" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -2508,6 +2922,9 @@
       <c r="C138" s="3" t="n">
         <v>49.06</v>
       </c>
+      <c r="D138" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -2523,6 +2940,9 @@
       <c r="C139" s="3" t="n">
         <v>8.49</v>
       </c>
+      <c r="D139" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -2536,7 +2956,10 @@
         </is>
       </c>
       <c r="C140" s="3" t="n">
-        <v>49.81</v>
+        <v>49.84</v>
+      </c>
+      <c r="D140" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="141">
@@ -2551,7 +2974,10 @@
         </is>
       </c>
       <c r="C141" s="3" t="n">
-        <v>50.28</v>
+        <v>50.3</v>
+      </c>
+      <c r="D141" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="142">
@@ -2566,7 +2992,10 @@
         </is>
       </c>
       <c r="C142" s="3" t="n">
-        <v>19.15</v>
+        <v>19.17</v>
+      </c>
+      <c r="D142" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="143">
@@ -2581,7 +3010,10 @@
         </is>
       </c>
       <c r="C143" s="3" t="n">
-        <v>32.28</v>
+        <v>32.31</v>
+      </c>
+      <c r="D143" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="144">
@@ -2598,6 +3030,9 @@
       <c r="C144" s="3" t="n">
         <v>0.88</v>
       </c>
+      <c r="D144" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -2613,6 +3048,9 @@
       <c r="C145" s="3" t="n">
         <v>12.13</v>
       </c>
+      <c r="D145" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -2628,6 +3066,9 @@
       <c r="C146" s="3" t="n">
         <v>9.98</v>
       </c>
+      <c r="D146" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -2643,6 +3084,9 @@
       <c r="C147" s="3" t="n">
         <v>1.03</v>
       </c>
+      <c r="D147" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -2658,6 +3102,9 @@
       <c r="C148" s="3" t="n">
         <v>98.15000000000001</v>
       </c>
+      <c r="D148" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
@@ -2673,6 +3120,9 @@
       <c r="C149" s="3" t="n">
         <v>3.06</v>
       </c>
+      <c r="D149" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -2688,6 +3138,9 @@
       <c r="C150" s="3" t="n">
         <v>7.62</v>
       </c>
+      <c r="D150" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -2703,6 +3156,9 @@
       <c r="C151" s="3" t="n">
         <v>2.89</v>
       </c>
+      <c r="D151" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -2718,6 +3174,9 @@
       <c r="C152" s="3" t="n">
         <v>2.32</v>
       </c>
+      <c r="D152" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
@@ -2733,6 +3192,9 @@
       <c r="C153" s="3" t="n">
         <v>2.83</v>
       </c>
+      <c r="D153" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
@@ -2748,6 +3210,9 @@
       <c r="C154" s="3" t="n">
         <v>1.77</v>
       </c>
+      <c r="D154" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
@@ -2763,6 +3228,9 @@
       <c r="C155" s="3" t="n">
         <v>1.72</v>
       </c>
+      <c r="D155" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
@@ -2778,6 +3246,9 @@
       <c r="C156" s="3" t="n">
         <v>4.81</v>
       </c>
+      <c r="D156" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
@@ -2793,6 +3264,9 @@
       <c r="C157" s="3" t="n">
         <v>2.01</v>
       </c>
+      <c r="D157" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
@@ -2808,6 +3282,9 @@
       <c r="C158" s="3" t="n">
         <v>2.25</v>
       </c>
+      <c r="D158" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
@@ -2823,6 +3300,9 @@
       <c r="C159" s="3" t="n">
         <v>8.84</v>
       </c>
+      <c r="D159" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
@@ -2838,6 +3318,9 @@
       <c r="C160" s="3" t="n">
         <v>5.5</v>
       </c>
+      <c r="D160" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
@@ -2853,6 +3336,9 @@
       <c r="C161" s="3" t="n">
         <v>25.05</v>
       </c>
+      <c r="D161" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
@@ -2868,6 +3354,9 @@
       <c r="C162" s="3" t="n">
         <v>1.33</v>
       </c>
+      <c r="D162" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
@@ -2883,6 +3372,9 @@
       <c r="C163" s="3" t="n">
         <v>1.03</v>
       </c>
+      <c r="D163" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
@@ -2898,6 +3390,9 @@
       <c r="C164" s="3" t="n">
         <v>4.64</v>
       </c>
+      <c r="D164" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
@@ -2913,6 +3408,9 @@
       <c r="C165" s="3" t="n">
         <v>2.21</v>
       </c>
+      <c r="D165" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
@@ -2926,7 +3424,10 @@
         </is>
       </c>
       <c r="C166" s="3" t="n">
-        <v>8.99</v>
+        <v>8.98</v>
+      </c>
+      <c r="D166" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="167">
@@ -2943,6 +3444,9 @@
       <c r="C167" s="3" t="n">
         <v>7.89</v>
       </c>
+      <c r="D167" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
@@ -2958,6 +3462,9 @@
       <c r="C168" s="3" t="n">
         <v>2.41</v>
       </c>
+      <c r="D168" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
@@ -2971,7 +3478,10 @@
         </is>
       </c>
       <c r="C169" s="3" t="n">
-        <v>4.25</v>
+        <v>4.24</v>
+      </c>
+      <c r="D169" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="170">
@@ -2986,7 +3496,10 @@
         </is>
       </c>
       <c r="C170" s="3" t="n">
-        <v>131.19</v>
+        <v>131.21</v>
+      </c>
+      <c r="D170" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="171">
@@ -3003,6 +3516,9 @@
       <c r="C171" s="3" t="n">
         <v>52.41</v>
       </c>
+      <c r="D171" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
@@ -3016,7 +3532,10 @@
         </is>
       </c>
       <c r="C172" s="3" t="n">
-        <v>28.35</v>
+        <v>28.38</v>
+      </c>
+      <c r="D172" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="173">
@@ -3033,6 +3552,9 @@
       <c r="C173" s="3" t="n">
         <v>1.48</v>
       </c>
+      <c r="D173" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
@@ -3048,6 +3570,9 @@
       <c r="C174" s="3" t="n">
         <v>25.82</v>
       </c>
+      <c r="D174" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
@@ -3063,6 +3588,9 @@
       <c r="C175" s="3" t="n">
         <v>3.23</v>
       </c>
+      <c r="D175" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
@@ -3078,6 +3606,9 @@
       <c r="C176" s="3" t="n">
         <v>1.48</v>
       </c>
+      <c r="D176" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
@@ -3093,6 +3624,9 @@
       <c r="C177" s="3" t="n">
         <v>0.96</v>
       </c>
+      <c r="D177" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
@@ -3108,6 +3642,9 @@
       <c r="C178" s="3" t="n">
         <v>1.36</v>
       </c>
+      <c r="D178" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
@@ -3121,7 +3658,10 @@
         </is>
       </c>
       <c r="C179" s="3" t="n">
-        <v>29.98</v>
+        <v>30</v>
+      </c>
+      <c r="D179" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="180">
@@ -3136,7 +3676,10 @@
         </is>
       </c>
       <c r="C180" s="3" t="n">
-        <v>13.94</v>
+        <v>13.96</v>
+      </c>
+      <c r="D180" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="181">
@@ -3153,6 +3696,9 @@
       <c r="C181" s="3" t="n">
         <v>4.66</v>
       </c>
+      <c r="D181" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
@@ -3166,7 +3712,10 @@
         </is>
       </c>
       <c r="C182" s="3" t="n">
-        <v>68.23</v>
+        <v>68.25</v>
+      </c>
+      <c r="D182" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="183">
@@ -3183,6 +3732,9 @@
       <c r="C183" s="3" t="n">
         <v>2</v>
       </c>
+      <c r="D183" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
@@ -3198,6 +3750,9 @@
       <c r="C184" s="3" t="n">
         <v>1.9</v>
       </c>
+      <c r="D184" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
@@ -3213,6 +3768,9 @@
       <c r="C185" s="3" t="n">
         <v>5.96</v>
       </c>
+      <c r="D185" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
@@ -3228,6 +3786,9 @@
       <c r="C186" s="3" t="n">
         <v>2.71</v>
       </c>
+      <c r="D186" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
@@ -3243,6 +3804,9 @@
       <c r="C187" s="3" t="n">
         <v>1.12</v>
       </c>
+      <c r="D187" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
@@ -3258,6 +3822,9 @@
       <c r="C188" s="3" t="n">
         <v>7.42</v>
       </c>
+      <c r="D188" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
@@ -3273,6 +3840,9 @@
       <c r="C189" s="3" t="n">
         <v>4.7</v>
       </c>
+      <c r="D189" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
@@ -3288,6 +3858,9 @@
       <c r="C190" s="3" t="n">
         <v>6.21</v>
       </c>
+      <c r="D190" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
@@ -3303,6 +3876,9 @@
       <c r="C191" s="3" t="n">
         <v>2.34</v>
       </c>
+      <c r="D191" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
@@ -3318,6 +3894,9 @@
       <c r="C192" s="3" t="n">
         <v>3.21</v>
       </c>
+      <c r="D192" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
@@ -3333,6 +3912,9 @@
       <c r="C193" s="3" t="n">
         <v>2.46</v>
       </c>
+      <c r="D193" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
@@ -3348,6 +3930,9 @@
       <c r="C194" s="3" t="n">
         <v>1.69</v>
       </c>
+      <c r="D194" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
@@ -3363,6 +3948,9 @@
       <c r="C195" s="3" t="n">
         <v>1.03</v>
       </c>
+      <c r="D195" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
@@ -3378,6 +3966,9 @@
       <c r="C196" s="3" t="n">
         <v>8.93</v>
       </c>
+      <c r="D196" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
@@ -3393,6 +3984,9 @@
       <c r="C197" s="3" t="n">
         <v>1.93</v>
       </c>
+      <c r="D197" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
@@ -3408,6 +4002,9 @@
       <c r="C198" s="3" t="n">
         <v>1.5</v>
       </c>
+      <c r="D198" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
@@ -3423,6 +4020,9 @@
       <c r="C199" s="3" t="n">
         <v>2.35</v>
       </c>
+      <c r="D199" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
@@ -3438,6 +4038,9 @@
       <c r="C200" s="3" t="n">
         <v>4.81</v>
       </c>
+      <c r="D200" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
@@ -3453,9 +4056,12 @@
       <c r="C201" s="3" t="n">
         <v>5.64</v>
       </c>
+      <c r="D201" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C201"/>
+  <autoFilter ref="A1:D201"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>